--- a/lp_tracker_formatted.xlsx
+++ b/lp_tracker_formatted.xlsx
@@ -74,6 +74,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00021544"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00888780"/>
       <sz val="10"/>
     </font>
@@ -94,12 +100,6 @@
       <b val="1"/>
       <color rgb="00378ADD"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00021544"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -303,30 +303,30 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -894,27 +894,27 @@
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L3" s="12" t="inlineStr">
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="M3" s="13" t="inlineStr">
-        <is>
-          <t>Form 6dbef1e</t>
+      <c r="M3" s="14" t="inlineStr">
+        <is>
+          <t>Apr=13 May=1</t>
         </is>
       </c>
     </row>
@@ -961,27 +961,27 @@
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L4" s="12" t="inlineStr">
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Revamped 2026-05-25</t>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>Apr=8 May=1</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
           <t>Flavours POS for Restaurants</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr"/>
+      <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
           <t>https://lp.qoyod.com/?page_id=558&amp;preview=true</t>
@@ -1012,37 +1012,37 @@
           <t>Draft</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="M5" s="13" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1060,7 +1060,7 @@
           <t>Flavours POS Rebuilt (v2)</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr"/>
+      <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
           <t>https://lp.qoyod.com/?page_id=840&amp;preview=true</t>
@@ -1071,60 +1071,60 @@
           <t>Draft</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="M6" s="13" t="inlineStr">
+      <c r="M6" s="14" t="inlineStr">
         <is>
           <t>Rebuilt 2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  Accounting</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="17" t="n"/>
-      <c r="H7" s="17" t="n"/>
-      <c r="I7" s="17" t="n"/>
-      <c r="J7" s="17" t="n"/>
-      <c r="K7" s="17" t="n"/>
-      <c r="L7" s="17" t="n"/>
-      <c r="M7" s="17" t="n"/>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n"/>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="18" t="n"/>
+      <c r="M7" s="18" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1132,7 +1132,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
@@ -1167,29 +1167,29 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K8" s="19" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="M8" s="13" t="inlineStr">
-        <is>
-          <t>Legacy live — highest traffic</t>
+      <c r="M8" s="14" t="inlineStr">
+        <is>
+          <t>Apr=29 — highest traffic</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
@@ -1209,7 +1209,7 @@
           <t>Accounting for Accountants</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr"/>
+      <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="8" t="inlineStr">
         <is>
           <t>https://lp.qoyod.com/?page_id=553&amp;preview=true</t>
@@ -1230,27 +1230,27 @@
           <t>Needed</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="M9" s="13" t="inlineStr">
+      <c r="M9" s="14" t="inlineStr">
         <is>
           <t>Rebuilt 2026-05-26</t>
         </is>
@@ -1262,7 +1262,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
@@ -1297,27 +1297,27 @@
           <t>Done 2026-06-09</t>
         </is>
       </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="M10" s="13" t="inlineStr">
+      <c r="M10" s="14" t="inlineStr">
         <is>
           <t>A/B base page</t>
         </is>
@@ -1383,29 +1383,29 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="M12" s="13" t="inlineStr">
-        <is>
-          <t>Legacy live</t>
+      <c r="M12" s="14" t="inlineStr">
+        <is>
+          <t>Legacy live — 2nd highest traffic</t>
         </is>
       </c>
     </row>
@@ -1450,27 +1450,27 @@
           <t>Done 2026-06-09</t>
         </is>
       </c>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="19" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="M13" s="13" t="inlineStr">
+      <c r="M13" s="14" t="inlineStr">
         <is>
           <t>Do NOT batch-upload</t>
         </is>
@@ -1511,7 +1511,7 @@
           <t>POS for Retail with ZATCA</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr"/>
+      <c r="D15" s="15" t="inlineStr"/>
       <c r="E15" s="8" t="inlineStr">
         <is>
           <t>https://lp.qoyod.com/?page_id=548&amp;preview=true</t>
@@ -1522,37 +1522,37 @@
           <t>Draft</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="M15" s="13" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1570,7 +1570,7 @@
           <t>Accounting for Retail</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr"/>
+      <c r="D16" s="15" t="inlineStr"/>
       <c r="E16" s="8" t="inlineStr">
         <is>
           <t>https://lp.qoyod.com/?page_id=559&amp;preview=true</t>
@@ -1591,27 +1591,27 @@
           <t>Needed</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L16" s="12" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="M16" s="13" t="inlineStr">
+      <c r="M16" s="14" t="inlineStr">
         <is>
           <t>Rebuilt 2026-05-26</t>
         </is>
@@ -1633,7 +1633,7 @@
           <t>Qoyod POS for Retail</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr"/>
+      <c r="D17" s="15" t="inlineStr"/>
       <c r="E17" s="8" t="inlineStr">
         <is>
           <t>https://lp.qoyod.com/?page_id=841&amp;preview=true</t>
@@ -1644,37 +1644,37 @@
           <t>Draft</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K17" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="M17" s="13" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="29" t="inlineStr">
@@ -1711,7 +1711,7 @@
           <t>Accounting for Services</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr"/>
+      <c r="D19" s="15" t="inlineStr"/>
       <c r="E19" s="8" t="inlineStr">
         <is>
           <t>https://lp.qoyod.com/?page_id=682&amp;preview=true</t>
@@ -1732,27 +1732,27 @@
           <t>Needed</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="M19" s="13" t="inlineStr">
+      <c r="M19" s="14" t="inlineStr">
         <is>
           <t>Rebuilt 2026-05-26</t>
         </is>
@@ -1799,27 +1799,27 @@
           <t>Done 2026-06-09</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="19" t="inlineStr">
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L20" s="12" t="inlineStr">
+      <c r="L20" s="13" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="M20" s="13" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -1837,7 +1837,7 @@
           <t>Accounting for Real Estate</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr"/>
+      <c r="D21" s="15" t="inlineStr"/>
       <c r="E21" s="8" t="inlineStr">
         <is>
           <t>https://lp.qoyod.com/?page_id=685&amp;preview=true</t>
@@ -1848,37 +1848,37 @@
           <t>Draft</t>
         </is>
       </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="M21" s="13" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="32" t="inlineStr">
@@ -1915,7 +1915,7 @@
           <t>Bookkeeping for Business Owners</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr"/>
+      <c r="D23" s="15" t="inlineStr"/>
       <c r="E23" s="8" t="inlineStr">
         <is>
           <t>https://lp.qoyod.com/?page_id=557&amp;preview=true</t>
@@ -1936,27 +1936,27 @@
           <t>Needed</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="12" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="M23" s="13" t="inlineStr">
+      <c r="M23" s="14" t="inlineStr">
         <is>
           <t>Rebuilt 2026-05-26</t>
         </is>
@@ -2022,27 +2022,27 @@
           <t>Done 2026-06-08</t>
         </is>
       </c>
-      <c r="I25" s="19" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J25" s="19" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K25" s="19" t="inlineStr">
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="L25" s="13" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="M25" s="13" t="inlineStr">
+      <c r="M25" s="14" t="inlineStr">
         <is>
           <t>All 6 mobile fixes</t>
         </is>

--- a/lp_tracker_formatted.xlsx
+++ b/lp_tracker_formatted.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,6 +100,18 @@
       <b val="1"/>
       <color rgb="00378ADD"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00042C53"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00173404"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -273,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -329,57 +341,63 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -747,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -761,8 +779,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -821,12 +841,22 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>HS Leads (30d)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>SQLs (30d)</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>WP Modified</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -850,6 +880,8 @@
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -907,14 +939,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="M3" s="14" t="inlineStr">
-        <is>
-          <t>Apr=13 May=1</t>
+      <c r="O3" s="14" t="inlineStr">
+        <is>
+          <t>Apr=13 May=1 / Snap instantforms</t>
         </is>
       </c>
     </row>
@@ -974,14 +1016,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
-        <is>
-          <t>Apr=8 May=1</t>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>Apr=8 May=1 / Snap instantforms</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1089,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L5" s="13" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr"/>
+      <c r="O5" s="14" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1096,12 +1158,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="M6" s="14" t="inlineStr">
+      <c r="O6" s="14" t="inlineStr">
         <is>
           <t>Rebuilt 2026-05-25</t>
         </is>
@@ -1125,6 +1197,8 @@
       <c r="K7" s="18" t="n"/>
       <c r="L7" s="18" t="n"/>
       <c r="M7" s="18" t="n"/>
+      <c r="N7" s="18" t="n"/>
+      <c r="O7" s="18" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1182,12 +1256,22 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="M8" s="14" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t>Apr=29 — highest traffic</t>
         </is>
@@ -1220,12 +1304,12 @@
           <t>Draft</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>qnav</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>Needed</t>
         </is>
@@ -1245,12 +1329,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="M9" s="14" t="inlineStr">
+      <c r="O9" s="14" t="inlineStr">
         <is>
           <t>Rebuilt 2026-05-26</t>
         </is>
@@ -1287,7 +1381,7 @@
           <t>Live</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>qnav</t>
         </is>
@@ -1312,35 +1406,47 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L10" s="13" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="M10" s="14" t="inlineStr">
+      <c r="O10" s="14" t="inlineStr">
         <is>
           <t>A/B base page</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Zatca</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
-      <c r="F11" s="23" t="n"/>
-      <c r="G11" s="23" t="n"/>
-      <c r="H11" s="23" t="n"/>
-      <c r="I11" s="23" t="n"/>
-      <c r="J11" s="23" t="n"/>
-      <c r="K11" s="23" t="n"/>
-      <c r="L11" s="23" t="n"/>
-      <c r="M11" s="23" t="n"/>
+      <c r="B11" s="25" t="n"/>
+      <c r="C11" s="25" t="n"/>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="25" t="n"/>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="25" t="n"/>
+      <c r="L11" s="25" t="n"/>
+      <c r="M11" s="25" t="n"/>
+      <c r="N11" s="25" t="n"/>
+      <c r="O11" s="25" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1348,7 +1454,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>ZATCA</t>
         </is>
@@ -1398,12 +1504,22 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L12" s="13" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="M12" s="14" t="inlineStr">
+      <c r="O12" s="14" t="inlineStr">
         <is>
           <t>Legacy live — 2nd highest traffic</t>
         </is>
@@ -1415,7 +1531,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>ZATCA</t>
         </is>
@@ -1440,7 +1556,7 @@
           <t>Live</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>qnav-dark</t>
         </is>
@@ -1465,35 +1581,47 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N13" s="13" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="M13" s="14" t="inlineStr">
+      <c r="O13" s="14" t="inlineStr">
         <is>
           <t>Do NOT batch-upload</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pos</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="27" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="27" t="n"/>
+      <c r="B14" s="29" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="29" t="n"/>
+      <c r="H14" s="29" t="n"/>
+      <c r="I14" s="29" t="n"/>
+      <c r="J14" s="29" t="n"/>
+      <c r="K14" s="29" t="n"/>
+      <c r="L14" s="29" t="n"/>
+      <c r="M14" s="29" t="n"/>
+      <c r="N14" s="29" t="n"/>
+      <c r="O14" s="29" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1501,7 +1629,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>POS / Retail</t>
         </is>
@@ -1547,12 +1675,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L15" s="13" t="inlineStr">
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="M15" s="14" t="inlineStr"/>
+      <c r="O15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1560,7 +1698,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>POS / Retail</t>
         </is>
@@ -1581,12 +1719,12 @@
           <t>Draft</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>qnav</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>Needed</t>
         </is>
@@ -1606,12 +1744,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L16" s="13" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="M16" s="14" t="inlineStr">
+      <c r="O16" s="14" t="inlineStr">
         <is>
           <t>Rebuilt 2026-05-26</t>
         </is>
@@ -1623,7 +1771,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>POS / Retail</t>
         </is>
@@ -1669,31 +1817,43 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L17" s="13" t="inlineStr">
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="M17" s="14" t="inlineStr"/>
+      <c r="O17" s="14" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Sector</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n"/>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="30" t="n"/>
-      <c r="H18" s="30" t="n"/>
-      <c r="I18" s="30" t="n"/>
-      <c r="J18" s="30" t="n"/>
-      <c r="K18" s="30" t="n"/>
-      <c r="L18" s="30" t="n"/>
-      <c r="M18" s="30" t="n"/>
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="32" t="n"/>
+      <c r="H18" s="32" t="n"/>
+      <c r="I18" s="32" t="n"/>
+      <c r="J18" s="32" t="n"/>
+      <c r="K18" s="32" t="n"/>
+      <c r="L18" s="32" t="n"/>
+      <c r="M18" s="32" t="n"/>
+      <c r="N18" s="32" t="n"/>
+      <c r="O18" s="32" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -1701,7 +1861,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
@@ -1722,12 +1882,12 @@
           <t>Draft</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>qnav</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>Needed</t>
         </is>
@@ -1747,12 +1907,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L19" s="13" t="inlineStr">
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="M19" s="14" t="inlineStr">
+      <c r="O19" s="14" t="inlineStr">
         <is>
           <t>Rebuilt 2026-05-26</t>
         </is>
@@ -1764,7 +1934,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="B20" s="31" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
@@ -1789,7 +1959,7 @@
           <t>Live</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>qnav</t>
         </is>
@@ -1814,12 +1984,26 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L20" s="13" t="inlineStr">
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="13" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="M20" s="14" t="inlineStr"/>
+      <c r="O20" s="14" t="inlineStr">
+        <is>
+          <t>HubSpot form, no WP LP ads</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -1827,7 +2011,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
@@ -1873,31 +2057,43 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L21" s="13" t="inlineStr">
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="M21" s="14" t="inlineStr"/>
+      <c r="O21" s="14" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="32" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Bookkeeping</t>
         </is>
       </c>
-      <c r="B22" s="33" t="n"/>
-      <c r="C22" s="33" t="n"/>
-      <c r="D22" s="33" t="n"/>
-      <c r="E22" s="33" t="n"/>
-      <c r="F22" s="33" t="n"/>
-      <c r="G22" s="33" t="n"/>
-      <c r="H22" s="33" t="n"/>
-      <c r="I22" s="33" t="n"/>
-      <c r="J22" s="33" t="n"/>
-      <c r="K22" s="33" t="n"/>
-      <c r="L22" s="33" t="n"/>
-      <c r="M22" s="33" t="n"/>
+      <c r="B22" s="35" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="35" t="n"/>
+      <c r="H22" s="35" t="n"/>
+      <c r="I22" s="35" t="n"/>
+      <c r="J22" s="35" t="n"/>
+      <c r="K22" s="35" t="n"/>
+      <c r="L22" s="35" t="n"/>
+      <c r="M22" s="35" t="n"/>
+      <c r="N22" s="35" t="n"/>
+      <c r="O22" s="35" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -1905,7 +2101,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>Bookkeeping</t>
         </is>
@@ -1926,12 +2122,12 @@
           <t>Draft</t>
         </is>
       </c>
-      <c r="G23" s="20" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>qnav</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>Needed</t>
         </is>
@@ -1951,35 +2147,47 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L23" s="13" t="inlineStr">
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="13" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="M23" s="14" t="inlineStr">
+      <c r="O23" s="14" t="inlineStr">
         <is>
           <t>Rebuilt 2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  Other</t>
         </is>
       </c>
-      <c r="B24" s="36" t="n"/>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
-      <c r="I24" s="36" t="n"/>
-      <c r="J24" s="36" t="n"/>
-      <c r="K24" s="36" t="n"/>
-      <c r="L24" s="36" t="n"/>
-      <c r="M24" s="36" t="n"/>
+      <c r="B24" s="38" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="38" t="n"/>
+      <c r="E24" s="38" t="n"/>
+      <c r="F24" s="38" t="n"/>
+      <c r="G24" s="38" t="n"/>
+      <c r="H24" s="38" t="n"/>
+      <c r="I24" s="38" t="n"/>
+      <c r="J24" s="38" t="n"/>
+      <c r="K24" s="38" t="n"/>
+      <c r="L24" s="38" t="n"/>
+      <c r="M24" s="38" t="n"/>
+      <c r="N24" s="38" t="n"/>
+      <c r="O24" s="38" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -1987,7 +2195,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -2012,7 +2220,7 @@
           <t>Live</t>
         </is>
       </c>
-      <c r="G25" s="38" t="inlineStr">
+      <c r="G25" s="40" t="inlineStr">
         <is>
           <t>qnav-mega</t>
         </is>
@@ -2037,154 +2245,203 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L25" s="13" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N25" s="13" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="M25" s="14" t="inlineStr">
+      <c r="O25" s="14" t="inlineStr">
         <is>
           <t>All 6 mobile fixes</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="39" t="inlineStr">
+      <c r="A26" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  Summary</t>
         </is>
       </c>
-      <c r="B26" s="40" t="n"/>
-      <c r="C26" s="40" t="n"/>
-      <c r="D26" s="40" t="n"/>
-      <c r="E26" s="40" t="n"/>
-      <c r="F26" s="40" t="n"/>
-      <c r="G26" s="40" t="n"/>
-      <c r="H26" s="40" t="n"/>
-      <c r="I26" s="40" t="n"/>
-      <c r="J26" s="40" t="n"/>
-      <c r="K26" s="40" t="n"/>
-      <c r="L26" s="40" t="n"/>
-      <c r="M26" s="40" t="n"/>
+      <c r="B26" s="42" t="n"/>
+      <c r="C26" s="42" t="n"/>
+      <c r="D26" s="42" t="n"/>
+      <c r="E26" s="42" t="n"/>
+      <c r="F26" s="42" t="n"/>
+      <c r="G26" s="42" t="n"/>
+      <c r="H26" s="42" t="n"/>
+      <c r="I26" s="42" t="n"/>
+      <c r="J26" s="42" t="n"/>
+      <c r="K26" s="42" t="n"/>
+      <c r="L26" s="42" t="n"/>
+      <c r="M26" s="42" t="n"/>
+      <c r="N26" s="42" t="n"/>
+      <c r="O26" s="42" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="41" t="inlineStr">
+      <c r="A27" s="43" t="inlineStr">
         <is>
           <t>Live pages</t>
         </is>
       </c>
-      <c r="B27" s="41" t="inlineStr">
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C27" s="41" t="inlineStr">
+      <c r="C27" s="43" t="inlineStr">
         <is>
           <t>303 / 463 / 683 / 773 / 850 / 851 / 8 / 240</t>
         </is>
       </c>
-      <c r="D27" s="41" t="n"/>
-      <c r="E27" s="41" t="n"/>
-      <c r="F27" s="41" t="n"/>
-      <c r="G27" s="41" t="n"/>
-      <c r="H27" s="41" t="n"/>
-      <c r="I27" s="41" t="n"/>
-      <c r="J27" s="41" t="n"/>
-      <c r="K27" s="41" t="n"/>
-      <c r="L27" s="41" t="n"/>
-      <c r="M27" s="41" t="n"/>
+      <c r="D27" s="43" t="n"/>
+      <c r="E27" s="43" t="n"/>
+      <c r="F27" s="43" t="n"/>
+      <c r="G27" s="43" t="n"/>
+      <c r="H27" s="43" t="n"/>
+      <c r="I27" s="43" t="n"/>
+      <c r="J27" s="43" t="n"/>
+      <c r="K27" s="43" t="n"/>
+      <c r="L27" s="43" t="n"/>
+      <c r="M27" s="43" t="n"/>
+      <c r="N27" s="43" t="n"/>
+      <c r="O27" s="43" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="41" t="inlineStr">
+      <c r="A28" s="43" t="inlineStr">
         <is>
           <t>Draft pages</t>
         </is>
       </c>
-      <c r="B28" s="41" t="inlineStr">
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C28" s="41" t="inlineStr">
+      <c r="C28" s="43" t="inlineStr">
         <is>
           <t>548 / 553 / 557 / 558 / 559 / 682 / 685 / 840 / 841</t>
         </is>
       </c>
-      <c r="D28" s="41" t="n"/>
-      <c r="E28" s="41" t="n"/>
-      <c r="F28" s="41" t="n"/>
-      <c r="G28" s="41" t="n"/>
-      <c r="H28" s="41" t="n"/>
-      <c r="I28" s="41" t="n"/>
-      <c r="J28" s="41" t="n"/>
-      <c r="K28" s="41" t="n"/>
-      <c r="L28" s="41" t="n"/>
-      <c r="M28" s="41" t="n"/>
+      <c r="D28" s="43" t="n"/>
+      <c r="E28" s="43" t="n"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="43" t="n"/>
+      <c r="H28" s="43" t="n"/>
+      <c r="I28" s="43" t="n"/>
+      <c r="J28" s="43" t="n"/>
+      <c r="K28" s="43" t="n"/>
+      <c r="L28" s="43" t="n"/>
+      <c r="M28" s="43" t="n"/>
+      <c r="N28" s="43" t="n"/>
+      <c r="O28" s="43" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="41" t="inlineStr">
+      <c r="A29" s="43" t="inlineStr">
         <is>
           <t>Mobile Fix Done</t>
         </is>
       </c>
-      <c r="B29" s="41" t="inlineStr">
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C29" s="41" t="inlineStr">
+      <c r="C29" s="43" t="inlineStr">
         <is>
           <t>tech-sector / accounting-system / zatca-einvoice / qawaem</t>
         </is>
       </c>
-      <c r="D29" s="41" t="n"/>
-      <c r="E29" s="41" t="n"/>
-      <c r="F29" s="41" t="n"/>
-      <c r="G29" s="41" t="n"/>
-      <c r="H29" s="41" t="n"/>
-      <c r="I29" s="41" t="n"/>
-      <c r="J29" s="41" t="n"/>
-      <c r="K29" s="41" t="n"/>
-      <c r="L29" s="41" t="n"/>
-      <c r="M29" s="41" t="n"/>
+      <c r="D29" s="43" t="n"/>
+      <c r="E29" s="43" t="n"/>
+      <c r="F29" s="43" t="n"/>
+      <c r="G29" s="43" t="n"/>
+      <c r="H29" s="43" t="n"/>
+      <c r="I29" s="43" t="n"/>
+      <c r="J29" s="43" t="n"/>
+      <c r="K29" s="43" t="n"/>
+      <c r="L29" s="43" t="n"/>
+      <c r="M29" s="43" t="n"/>
+      <c r="N29" s="43" t="n"/>
+      <c r="O29" s="43" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="41" t="inlineStr">
+      <c r="A30" s="43" t="inlineStr">
         <is>
           <t>Mobile Fix Needed</t>
         </is>
       </c>
-      <c r="B30" s="41" t="inlineStr">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C30" s="41" t="inlineStr">
+      <c r="C30" s="43" t="inlineStr">
         <is>
           <t>accounting-accountants / retail-accounting / services-sector / bookkeeping-smb</t>
         </is>
       </c>
-      <c r="D30" s="41" t="n"/>
-      <c r="E30" s="41" t="n"/>
-      <c r="F30" s="41" t="n"/>
-      <c r="G30" s="41" t="n"/>
-      <c r="H30" s="41" t="n"/>
-      <c r="I30" s="41" t="n"/>
-      <c r="J30" s="41" t="n"/>
-      <c r="K30" s="41" t="n"/>
-      <c r="L30" s="41" t="n"/>
-      <c r="M30" s="41" t="n"/>
+      <c r="D30" s="43" t="n"/>
+      <c r="E30" s="43" t="n"/>
+      <c r="F30" s="43" t="n"/>
+      <c r="G30" s="43" t="n"/>
+      <c r="H30" s="43" t="n"/>
+      <c r="I30" s="43" t="n"/>
+      <c r="J30" s="43" t="n"/>
+      <c r="K30" s="43" t="n"/>
+      <c r="L30" s="43" t="n"/>
+      <c r="M30" s="43" t="n"/>
+      <c r="N30" s="43" t="n"/>
+      <c r="O30" s="43" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>HS Leads source</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>last 30d</t>
+        </is>
+      </c>
+      <c r="C31" s="43" t="inlineStr">
+        <is>
+          <t>Google + Bing paid search → _WP utm_content ads only</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="n"/>
+      <c r="E31" s="43" t="n"/>
+      <c r="F31" s="43" t="n"/>
+      <c r="G31" s="43" t="n"/>
+      <c r="H31" s="43" t="n"/>
+      <c r="I31" s="43" t="n"/>
+      <c r="J31" s="43" t="n"/>
+      <c r="K31" s="43" t="n"/>
+      <c r="L31" s="43" t="n"/>
+      <c r="M31" s="43" t="n"/>
+      <c r="N31" s="43" t="n"/>
+      <c r="O31" s="43" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A7:O7"/>
+    <mergeCell ref="A26:O26"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="A18:O18"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
